--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:04:23+00:00</t>
+    <t>2026-10-15T15:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:21:59+00:00</t>
+    <t>2026-10-15T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
